--- a/cds_files/TexasTech_CDS_2024-2025.xlsx
+++ b/cds_files/TexasTech_CDS_2024-2025.xlsx
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32580</v>
+        <v>32394</v>
       </c>
     </row>
     <row r="5">
